--- a/data.mn/public/datasets/mongolbank-credit-private-sector.xlsx
+++ b/data.mn/public/datasets/mongolbank-credit-private-sector.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3141,6 +3141,26 @@
       </c>
       <c r="B272" t="n">
         <v>19103.76</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>19076.93</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>19460.16</v>
       </c>
     </row>
   </sheetData>
@@ -3154,7 +3174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5883,6 +5903,26 @@
         <v>19103.76</v>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>19076.93</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>19460.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
